--- a/output/EN_All_Vasai_Wada_merged_Checking_Ok_FINAL.xlsx
+++ b/output/EN_All_Vasai_Wada_merged_Checking_Ok_FINAL.xlsx
@@ -2329,7 +2329,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Ramadas C S</t>
+          <t>Ramadas C. S.</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>Nayar Ara.Ke.</t>
+          <t>Nayar R. K.</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Nayar Si.Esa.</t>
+          <t>Nayar C. S.</t>
         </is>
       </c>
     </row>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>Sabu Ti.Jon</t>
+          <t>Sabu TJon</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Chavala Ke.Ke</t>
+          <t>Chavala KKe</t>
         </is>
       </c>
     </row>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>Chavala Ke.Ke.</t>
+          <t>Chavala K. K.</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>Chavala Ke.Ke.</t>
+          <t>Chavala K. K.</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>Ponnat Ti.Ke.</t>
+          <t>Ponnat T. K.</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>Ponnat Madhavan Ti.Ke.</t>
+          <t>Ponnat Madhavan T. K.</t>
         </is>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>Pujari Ke.Ti.</t>
+          <t>Pujari K. T.</t>
         </is>
       </c>
     </row>
@@ -12071,7 +12071,7 @@
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>Pujari Ke.Ti.</t>
+          <t>Pujari K. T.</t>
         </is>
       </c>
     </row>
@@ -12143,7 +12143,7 @@
       </c>
       <c r="Q163" t="inlineStr">
         <is>
-          <t>Pujari Ke.Ti.</t>
+          <t>Pujari K. T.</t>
         </is>
       </c>
     </row>
@@ -12205,7 +12205,7 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Nageshaprasad Pujari Ke.Ti.</t>
+          <t>Nageshaprasad Pujari K. T.</t>
         </is>
       </c>
     </row>
@@ -20288,7 +20288,7 @@
       </c>
       <c r="Q278" t="inlineStr">
         <is>
-          <t>Rav Pi.Bi.</t>
+          <t>Rav P. B.</t>
         </is>
       </c>
     </row>
@@ -20360,7 +20360,7 @@
       </c>
       <c r="Q279" t="inlineStr">
         <is>
-          <t>Rav Pi.Vi.</t>
+          <t>Rav PVi.</t>
         </is>
       </c>
     </row>
@@ -20715,7 +20715,7 @@
       </c>
       <c r="Q284" t="inlineStr">
         <is>
-          <t>Sing E.Ema.</t>
+          <t>Sing A. M.</t>
         </is>
       </c>
     </row>
@@ -20787,7 +20787,7 @@
       </c>
       <c r="Q285" t="inlineStr">
         <is>
-          <t>Sing E.Ema.</t>
+          <t>Sing A. M.</t>
         </is>
       </c>
     </row>
@@ -20859,7 +20859,7 @@
       </c>
       <c r="Q286" t="inlineStr">
         <is>
-          <t>Sing E.Ema.</t>
+          <t>Sing A. M.</t>
         </is>
       </c>
     </row>
@@ -23878,7 +23878,7 @@
       </c>
       <c r="P328" t="inlineStr">
         <is>
-          <t>Yadav S B</t>
+          <t>Yadav S. B.</t>
         </is>
       </c>
       <c r="Q328" t="inlineStr">
@@ -23955,7 +23955,7 @@
       </c>
       <c r="Q329" t="inlineStr">
         <is>
-          <t>Yadav Esa.Vi.</t>
+          <t>Yadav SVi.</t>
         </is>
       </c>
     </row>
@@ -24968,7 +24968,7 @@
       </c>
       <c r="Q343" t="inlineStr">
         <is>
-          <t>Agaraval Esa.Ke.</t>
+          <t>Agaraval S. K.</t>
         </is>
       </c>
     </row>
@@ -28168,7 +28168,7 @@
       </c>
       <c r="P388" t="inlineStr">
         <is>
-          <t>Pachu Sunil Kepi.</t>
+          <t>Pachu Sunil Kep.</t>
         </is>
       </c>
     </row>
@@ -30658,7 +30658,7 @@
       </c>
       <c r="Q423" t="inlineStr">
         <is>
-          <t>Paramar Je.Ke.</t>
+          <t>Paramar J. K.</t>
         </is>
       </c>
     </row>
